--- a/examples/Nusinersen/CEREBRO_X_Completed_Data_Nusinersen.xlsx
+++ b/examples/Nusinersen/CEREBRO_X_Completed_Data_Nusinersen.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-05T08:06:05Z  | Pipeline: v20  | Source: CEREBRO_Input_Nusinersen.xlsx</t>
+          <t>Generated: 2026-09-05T18:07:25Z  | Pipeline: v20  | Source: CEREBRO_Input_Nusinersen.xlsx</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="U4" s="28" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V4" s="28" t="n">
         <v>0</v>
@@ -14043,7 +14043,7 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -14284,7 +14284,7 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -14525,7 +14525,7 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -15248,7 +15248,7 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -15489,7 +15489,7 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>5464.63</v>
+        <v>5737.65</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
